--- a/csv/model/DCC/formula_DCC_AB.xlsx
+++ b/csv/model/DCC/formula_DCC_AB.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32175" yWindow="990" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M230" t="n">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M233" t="n">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -18415,7 +18415,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -18818,7 +18818,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -18999,7 +18999,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -19847,7 +19847,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -20425,7 +20425,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21046,7 +21046,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -21800,7 +21800,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -21927,7 +21927,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22325,7 +22325,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22410,7 +22410,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -22501,7 +22501,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -22713,7 +22713,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -22798,7 +22798,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -22889,7 +22889,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23101,7 +23101,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23277,7 +23277,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -23665,7 +23665,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -23962,7 +23962,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24138,7 +24138,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24265,7 +24265,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24441,7 +24441,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -24653,7 +24653,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -25126,7 +25126,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25302,7 +25302,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25429,7 +25429,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -25605,7 +25605,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -25690,7 +25690,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -25817,7 +25817,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -26078,7 +26078,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26381,7 +26381,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26466,7 +26466,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -26593,7 +26593,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -26678,7 +26678,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27242,7 +27242,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -27284,7 +27284,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -27757,7 +27757,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -27842,7 +27842,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -27933,7 +27933,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -28018,7 +28018,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -28145,7 +28145,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -28448,7 +28448,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -28533,7 +28533,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -28618,7 +28618,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -28709,7 +28709,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -28794,7 +28794,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
